--- a/Result/profitability/3576.xlsx
+++ b/Result/profitability/3576.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05750000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.9625</v>
+        <v>-11.9975</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.40625</v>
+        <v>0.40375</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.199999999999999</v>
+        <v>-14.88125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.87125</v>
+        <v>0.86625</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.1625</v>
+        <v>-12.36625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9037500000000001</v>
+        <v>0.9175</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.70875</v>
+        <v>-9.672499999999998</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.67</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6025</v>
+        <v>0.61625</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.5375</v>
+        <v>-6.729999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0.32125</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.904999999999998</v>
+        <v>-7.412499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>0.42375</v>
+        <v>0.2725</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.374999999999999</v>
+        <v>-0.522499999999998</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06499999999999997</v>
+        <v>0.06499999999999996</v>
       </c>
       <c r="N10" t="n">
         <v>2.796250000000002</v>
@@ -9352,13 +9352,13 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="J71" t="n">
-        <v>-429</v>
+        <v>-416</v>
       </c>
       <c r="K71" t="n">
-        <v>-431</v>
+        <v>-420</v>
       </c>
       <c r="L71" t="n">
         <v>-0.26</v>
@@ -9479,19 +9479,19 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="J72" t="n">
-        <v>-410</v>
+        <v>-423</v>
       </c>
       <c r="K72" t="n">
-        <v>-411</v>
+        <v>-422</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.4075</v>
+        <v>-0.40875</v>
       </c>
       <c r="N72" t="n">
         <v>-11.17125</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.01000000000000001</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.03846153846153855</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
         <v>-6.169999999999998</v>
@@ -9533,10 +9533,10 @@
         <v>0.1982647814910026</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.4897959183673469</v>
+        <v>-0.4693877551020408</v>
       </c>
       <c r="AC72" t="n">
         <v>-38.74</v>
@@ -9545,7 +9545,7 @@
         <v>-26.71724137931034</v>
       </c>
       <c r="AE72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
         <v>1</v>
@@ -9618,7 +9618,7 @@
         <v>-0.14</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.25875</v>
+        <v>-0.26</v>
       </c>
       <c r="N73" t="n">
         <v>-6.45125</v>
@@ -9648,10 +9648,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.4615384615384615</v>
       </c>
       <c r="Y73" t="n">
         <v>18.52</v>
@@ -9745,7 +9745,7 @@
         <v>1.07</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.10375</v>
+        <v>-0.105</v>
       </c>
       <c r="N74" t="n">
         <v>-11.59125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>758</v>
+      </c>
+      <c r="D75" t="n">
+        <v>810</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-52</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-263</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-34.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-229</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-230</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-13.09875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.130841121495327</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.8503833515881709</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4615384615384615</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7805269922879178</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
